--- a/output/2026-09-02_21_Italia_Molise_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-02_21_Italia_Molise_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -494,10 +494,9 @@
           <t>0874 62009 / 393 9254409</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore di forniture industriali (bulloneria, cuscinetti, utensileria, cinghie, saldatura, guarnizioni, pneumatica, lubrificanti); attiva dal 1990. Verificata tramite PagineGialle, Registroaziende e sito ufficiale.</t>
+          <t>Distributore di forniture industriali (bulloneria, cuscinetti, utensileria, cinghie, saldatura, guarnizioni, pneumatica, lubrificanti); attiva dal 1990. Verificata tramite PagineGialle, Registroaziende e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-02_16_Italia_Molise_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nonostante il nome, e' distributore di forniture agricole/industriali (motori elettrici, gruppi elettrogeni, compressori, cuscinetti, cinghie) dal 1944, non un'officina di produzione conto terzi. Verificato tramite Atoka/PagineBianche/sito ufficiale.</t>
+          <t>Nonostante il nome, e' distributore di forniture agricole/industriali (motori elettrici, gruppi elettrogeni, compressori, cuscinetti, cinghie) dal 1944, non un'officina di produzione conto terzi. Verificato tramite Atoka/PagineBianche/sito ufficiale. [DUPLICATO — vedi anche: 2026-09-02_15_Italia_Molise_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -596,7 +595,6 @@
           <t>Perrotti Francesco Vittorio</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Campobasso</t>
@@ -612,7 +610,6 @@
           <t>0874 484327</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Ferramenta industriale, acciai e metalli; presente su Europages e PagineGialle. Nessun sito web ufficiale reperito, nessuna email verificata: campi lasciati vuoti.</t>
@@ -650,10 +647,9 @@
           <t>0875 85429 / 0875 707360</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Distributore all'ingrosso di ferramenta industriale, utensileria, metallo duro, bulloneria, rivetteria, saldatura, pneumatica. Verificato tramite Europages e sito ufficiale.</t>
+          <t>Distributore all'ingrosso di ferramenta industriale, utensileria, metallo duro, bulloneria, rivetteria, saldatura, pneumatica. Verificato tramite Europages e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-02_18_Italia_Molise_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -710,7 +706,6 @@
           <t>Ferramenta Izzi Snc</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Isernia</t>
@@ -726,7 +721,6 @@
           <t>351 5429068</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Ferramenta e forniture industriali, vendita all'ingrosso. Verificato tramite Misterimprese/PagineBianche. Nessun sito web ufficiale reperito.</t>
@@ -744,7 +738,6 @@
           <t>Ferramenta E.G. di Peluso Emiliano e Rea Giuseppe S.n.c.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Isernia</t>
